--- a/artfynd/A 1752-2026 artfynd.xlsx
+++ b/artfynd/A 1752-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69018139</v>
+        <v>63189954</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storträsk, Vb</t>
+          <t>Brännliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734292.8805415184</v>
+        <v>733729</v>
       </c>
       <c r="R2" t="n">
-        <v>7237490.997055069</v>
+        <v>7237558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +764,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lokal-ID: 6 Box-ID: 6G</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,15 +789,112 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69018139</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>734293</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7237491</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-07-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Torbjörn Josefsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Torbjörn Josefsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 1752-2026 artfynd.xlsx
+++ b/artfynd/A 1752-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,8 +909,17 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018139</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>